--- a/hardware/expansion-board-v4/CHECKLIST-V4.8.xlsx
+++ b/hardware/expansion-board-v4/CHECKLIST-V4.8.xlsx
@@ -5498,7 +5498,7 @@
       </c>
       <c r="E175" s="10" t="inlineStr">
         <is>
-          <t>80.9, 87.3</t>
+          <t>80.9, 87.6</t>
         </is>
       </c>
       <c r="F175" s="12" t="inlineStr">

--- a/hardware/expansion-board-v4/CHECKLIST-V4.8.xlsx
+++ b/hardware/expansion-board-v4/CHECKLIST-V4.8.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G254"/>
+  <dimension ref="A1:G258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4922,90 +4922,90 @@
       </c>
       <c r="G153" s="5" t="inlineStr"/>
     </row>
-    <row r="154" ht="19" customHeight="1"/>
+    <row r="154" ht="19" customHeight="1">
+      <c r="A154" s="2" t="inlineStr"/>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>R64</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>1k</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>145.8, 80.3</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>A 电源</t>
+        </is>
+      </c>
+      <c r="G154" s="5" t="inlineStr"/>
+    </row>
     <row r="155" ht="19" customHeight="1">
       <c r="A155" s="2" t="inlineStr"/>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>R65</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>18nH 0402CS-18NXGRW</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>L_0402_1005Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>110.4, 59.8</t>
+          <t>145.8, 84.2</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>A 电源</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr"/>
     </row>
-    <row r="156" ht="19" customHeight="1">
-      <c r="A156" s="2" t="inlineStr"/>
-      <c r="B156" s="3" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>33nH</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr">
-        <is>
-          <t>L_0402_1005Metric</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t>57.7, 75.4</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>C 传感器 + GNSS</t>
-        </is>
-      </c>
-      <c r="G156" s="5" t="inlineStr"/>
-    </row>
+    <row r="156" ht="19" customHeight="1"/>
     <row r="157" ht="19" customHeight="1">
       <c r="A157" s="2" t="inlineStr"/>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>L7</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>6.8uH</t>
+          <t>18nH 0402CS-18NXGRW</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>L_0805_2012Metric</t>
+          <t>L_0402_1005Metric</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>97.3, 94.7</t>
+          <t>110.4, 59.8</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr"/>
@@ -5014,12 +5014,12 @@
       <c r="A158" s="2" t="inlineStr"/>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>L8</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>100nH</t>
+          <t>33nH</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>119.3, 90.3</t>
+          <t>57.7, 75.4</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr"/>
@@ -5043,22 +5043,22 @@
       <c r="A159" s="2" t="inlineStr"/>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L7</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>7.5nH</t>
+          <t>6.8uH</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>L_0402_1005Metric</t>
+          <t>L_0805_2012Metric</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>112.3, 94.8</t>
+          <t>97.3, 94.7</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
@@ -5072,12 +5072,12 @@
       <c r="A160" s="2" t="inlineStr"/>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>L10</t>
+          <t>L8</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>27nH</t>
+          <t>100nH</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>110.9, 95.7</t>
+          <t>119.3, 90.3</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
@@ -5101,12 +5101,12 @@
       <c r="A161" s="2" t="inlineStr"/>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>L11</t>
+          <t>L9</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>6.8nH</t>
+          <t>7.5nH</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>118.2, 97.5</t>
+          <t>112.3, 94.8</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
@@ -5130,12 +5130,12 @@
       <c r="A162" s="2" t="inlineStr"/>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>L12</t>
+          <t>L10</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>6.8nH</t>
+          <t>27nH</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>118.2, 95.2</t>
+          <t>110.9, 95.7</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
@@ -5159,12 +5159,12 @@
       <c r="A163" s="2" t="inlineStr"/>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>L13</t>
+          <t>L11</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>7.5nH</t>
+          <t>6.8nH</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>110.7, 92.2</t>
+          <t>118.2, 97.5</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
@@ -5188,12 +5188,12 @@
       <c r="A164" s="2" t="inlineStr"/>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>L14</t>
+          <t>L12</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>100nH</t>
+          <t>6.8nH</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>101.1, 70.6</t>
+          <t>118.2, 95.2</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>D 978 收发</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr"/>
@@ -5217,12 +5217,12 @@
       <c r="A165" s="2" t="inlineStr"/>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>L15</t>
+          <t>L13</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>33nH</t>
+          <t>7.5nH</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>57.6, 68.7</t>
+          <t>110.7, 92.2</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>D 978 收发</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr"/>
@@ -5246,27 +5246,27 @@
       <c r="A166" s="2" t="inlineStr"/>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>L16</t>
+          <t>L14</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>1uH</t>
+          <t>100nH</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>L_Bourns-SRN4018</t>
+          <t>L_0402_1005Metric</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>139.7, 83.6</t>
+          <t>101.1, 70.6</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>A 电源</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr"/>
@@ -5275,27 +5275,27 @@
       <c r="A167" s="2" t="inlineStr"/>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>L17</t>
+          <t>L15</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>4.7uH XEL4030-472MEC</t>
+          <t>33nH</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>L_Coilcraft_XxL4030</t>
+          <t>L_0402_1005Metric</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>144.8, 95.0</t>
+          <t>57.6, 68.7</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>A 电源</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr"/>
@@ -5304,95 +5304,95 @@
       <c r="A168" s="2" t="inlineStr"/>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>L18</t>
+          <t>L16</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>100nH</t>
+          <t>1uH</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>L_0402_1005Metric</t>
+          <t>L_Bourns-SRN4018</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>126.0, 93.9</t>
+          <t>139.7, 83.6</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>G 航空波段 AIRBAND</t>
+          <t>A 电源</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr"/>
     </row>
-    <row r="169" ht="19" customHeight="1"/>
+    <row r="169" ht="19" customHeight="1">
+      <c r="A169" s="2" t="inlineStr"/>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>L17</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>4.7uH XEL4030-472MEC</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>L_Coilcraft_XxL4030</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>144.8, 95.0</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>A 电源</t>
+        </is>
+      </c>
+      <c r="G169" s="5" t="inlineStr"/>
+    </row>
     <row r="170" ht="19" customHeight="1">
       <c r="A170" s="2" t="inlineStr"/>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>L18</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>TPESD8L3.3 0.3pFtyp 0.5pFmax</t>
+          <t>100nH</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>D_0402_1005Metric</t>
+          <t>L_0402_1005Metric</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>101.1, 72.6</t>
+          <t>126.0, 93.9</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>G 航空波段 AIRBAND</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr"/>
     </row>
-    <row r="171" ht="19" customHeight="1">
-      <c r="A171" s="2" t="inlineStr"/>
-      <c r="B171" s="3" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="C171" s="4" t="inlineStr">
-        <is>
-          <t>TPESD8L3.3 0.3pFtyp 0.5pFmax</t>
-        </is>
-      </c>
-      <c r="D171" s="4" t="inlineStr">
-        <is>
-          <t>D_0402_1005Metric</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
-        <is>
-          <t>117.5, 89.9</t>
-        </is>
-      </c>
-      <c r="F171" s="4" t="inlineStr">
-        <is>
-          <t>D 978 收发</t>
-        </is>
-      </c>
-      <c r="G171" s="5" t="inlineStr"/>
-    </row>
+    <row r="171" ht="19" customHeight="1"/>
     <row r="172" ht="19" customHeight="1">
       <c r="A172" s="2" t="inlineStr"/>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
@@ -5407,12 +5407,12 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>139.3, 75.4</t>
+          <t>101.1, 72.6</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>B MCU + Flash</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr"/>
@@ -5421,240 +5421,276 @@
       <c r="A173" s="2" t="inlineStr"/>
       <c r="B173" s="3" t="inlineStr">
         <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>TPESD8L3.3 0.3pFtyp 0.5pFmax</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>D_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>117.5, 89.9</t>
+        </is>
+      </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>D 978 收发</t>
+        </is>
+      </c>
+      <c r="G173" s="5" t="inlineStr"/>
+    </row>
+    <row r="174" ht="19" customHeight="1">
+      <c r="A174" s="2" t="inlineStr"/>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>TPESD8L3.3 0.3pFtyp 0.5pFmax</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>D_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>139.3, 75.4</t>
+        </is>
+      </c>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>B MCU + Flash</t>
+        </is>
+      </c>
+      <c r="G174" s="5" t="inlineStr"/>
+    </row>
+    <row r="175" ht="19" customHeight="1">
+      <c r="A175" s="2" t="inlineStr"/>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="C173" s="4" t="inlineStr">
+      <c r="C175" s="4" t="inlineStr">
         <is>
           <t>TPESD8L3.3 0.3pFtyp 0.5pFmax</t>
         </is>
       </c>
-      <c r="D173" s="4" t="inlineStr">
+      <c r="D175" s="4" t="inlineStr">
         <is>
           <t>D_0402_1005Metric</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>139.3, 77.8</t>
         </is>
       </c>
-      <c r="F173" s="4" t="inlineStr">
+      <c r="F175" s="4" t="inlineStr">
         <is>
           <t>B MCU + Flash</t>
         </is>
       </c>
-      <c r="G173" s="5" t="inlineStr"/>
-    </row>
-    <row r="174" ht="19" customHeight="1">
-      <c r="A174" s="10" t="inlineStr"/>
-      <c r="B174" s="11" t="inlineStr">
+      <c r="G175" s="5" t="inlineStr"/>
+    </row>
+    <row r="176" ht="19" customHeight="1">
+      <c r="A176" s="10" t="inlineStr"/>
+      <c r="B176" s="11" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="C174" s="12" t="inlineStr">
+      <c r="C176" s="12" t="inlineStr">
         <is>
           <t>TPESD8L3.3 0.3pFtyp 0.5pFmax</t>
         </is>
       </c>
-      <c r="D174" s="12" t="inlineStr">
+      <c r="D176" s="12" t="inlineStr">
         <is>
           <t>D_0402_1005Metric</t>
         </is>
       </c>
-      <c r="E174" s="10" t="inlineStr">
+      <c r="E176" s="10" t="inlineStr">
         <is>
           <t>126.4, 89.3</t>
         </is>
       </c>
-      <c r="F174" s="12" t="inlineStr">
+      <c r="F176" s="12" t="inlineStr">
         <is>
           <t>G 航空波段 AIRBAND</t>
         </is>
       </c>
-      <c r="G174" s="13" t="inlineStr">
+      <c r="G176" s="13" t="inlineStr">
         <is>
           <t>有极性，认阴极标记带</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="19" customHeight="1">
-      <c r="A175" s="10" t="inlineStr"/>
-      <c r="B175" s="11" t="inlineStr">
+    <row r="177" ht="19" customHeight="1">
+      <c r="A177" s="10" t="inlineStr"/>
+      <c r="B177" s="11" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
       </c>
-      <c r="C175" s="12" t="inlineStr">
+      <c r="C177" s="12" t="inlineStr">
         <is>
           <t>1N4148WS</t>
         </is>
       </c>
-      <c r="D175" s="12" t="inlineStr">
+      <c r="D177" s="12" t="inlineStr">
         <is>
           <t>D_SOD-323</t>
         </is>
       </c>
-      <c r="E175" s="10" t="inlineStr">
+      <c r="E177" s="10" t="inlineStr">
         <is>
           <t>80.9, 87.6</t>
         </is>
       </c>
-      <c r="F175" s="12" t="inlineStr">
+      <c r="F177" s="12" t="inlineStr">
         <is>
           <t>A 电源</t>
         </is>
       </c>
-      <c r="G175" s="13" t="inlineStr">
+      <c r="G177" s="13" t="inlineStr">
         <is>
           <t>有极性，认阴极标记带</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="19" customHeight="1"/>
-    <row r="177" ht="19" customHeight="1">
-      <c r="A177" s="2" t="inlineStr"/>
-      <c r="B177" s="3" t="inlineStr">
+    <row r="178" ht="19" customHeight="1">
+      <c r="A178" s="10" t="inlineStr"/>
+      <c r="B178" s="11" t="inlineStr">
+        <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="C178" s="12" t="inlineStr">
+        <is>
+          <t>LED 红/黄(Vf2.0-2.2)</t>
+        </is>
+      </c>
+      <c r="D178" s="12" t="inlineStr">
+        <is>
+          <t>LED_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="E178" s="10" t="inlineStr">
+        <is>
+          <t>148.5, 80.3</t>
+        </is>
+      </c>
+      <c r="F178" s="12" t="inlineStr">
+        <is>
+          <t>A 电源</t>
+        </is>
+      </c>
+      <c r="G178" s="13" t="inlineStr">
+        <is>
+          <t>有极性，认阴极标记带</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="19" customHeight="1">
+      <c r="A179" s="10" t="inlineStr"/>
+      <c r="B179" s="11" t="inlineStr">
+        <is>
+          <t>D9</t>
+        </is>
+      </c>
+      <c r="C179" s="12" t="inlineStr">
+        <is>
+          <t>LED 红/黄(Vf2.0-2.2)</t>
+        </is>
+      </c>
+      <c r="D179" s="12" t="inlineStr">
+        <is>
+          <t>LED_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="E179" s="10" t="inlineStr">
+        <is>
+          <t>148.5, 84.2</t>
+        </is>
+      </c>
+      <c r="F179" s="12" t="inlineStr">
+        <is>
+          <t>A 电源</t>
+        </is>
+      </c>
+      <c r="G179" s="13" t="inlineStr">
+        <is>
+          <t>有极性，认阴极标记带</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="19" customHeight="1"/>
+    <row r="181" ht="19" customHeight="1">
+      <c r="A181" s="2" t="inlineStr"/>
+      <c r="B181" s="3" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="C177" s="4" t="inlineStr">
+      <c r="C181" s="4" t="inlineStr">
         <is>
           <t>6V/200mA</t>
         </is>
       </c>
-      <c r="D177" s="4" t="inlineStr">
+      <c r="D181" s="4" t="inlineStr">
         <is>
           <t>Fuse_0805_2012Metric</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>122.0, 91.0</t>
         </is>
       </c>
-      <c r="F177" s="4" t="inlineStr">
+      <c r="F181" s="4" t="inlineStr">
         <is>
           <t>D 978 收发</t>
         </is>
       </c>
-      <c r="G177" s="5" t="inlineStr"/>
-    </row>
-    <row r="178" ht="19" customHeight="1">
-      <c r="A178" s="2" t="inlineStr"/>
-      <c r="B178" s="3" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="C178" s="4" t="inlineStr">
-        <is>
-          <t>6V/200mA</t>
-        </is>
-      </c>
-      <c r="D178" s="4" t="inlineStr">
-        <is>
-          <t>Fuse_0805_2012Metric</t>
-        </is>
-      </c>
-      <c r="E178" s="2" t="inlineStr">
-        <is>
-          <t>98.3, 71.7</t>
-        </is>
-      </c>
-      <c r="F178" s="4" t="inlineStr">
-        <is>
-          <t>E 1090 接收链</t>
-        </is>
-      </c>
-      <c r="G178" s="5" t="inlineStr"/>
-    </row>
-    <row r="179" ht="19" customHeight="1">
-      <c r="A179" s="2" t="inlineStr"/>
-      <c r="B179" s="3" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="C179" s="4" t="inlineStr">
-        <is>
-          <t>6V/200mA</t>
-        </is>
-      </c>
-      <c r="D179" s="4" t="inlineStr">
-        <is>
-          <t>Fuse_0805_2012Metric</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t>60.3, 75.9</t>
-        </is>
-      </c>
-      <c r="F179" s="4" t="inlineStr">
-        <is>
-          <t>C 传感器 + GNSS</t>
-        </is>
-      </c>
-      <c r="G179" s="5" t="inlineStr"/>
-    </row>
-    <row r="180" ht="19" customHeight="1">
-      <c r="A180" s="2" t="inlineStr"/>
-      <c r="B180" s="3" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="C180" s="4" t="inlineStr">
-        <is>
-          <t>6V/200mA</t>
-        </is>
-      </c>
-      <c r="D180" s="4" t="inlineStr">
-        <is>
-          <t>Fuse_0805_2012Metric</t>
-        </is>
-      </c>
-      <c r="E180" s="2" t="inlineStr">
-        <is>
-          <t>60.3, 69.2</t>
-        </is>
-      </c>
-      <c r="F180" s="4" t="inlineStr">
-        <is>
-          <t>C 传感器 + GNSS</t>
-        </is>
-      </c>
-      <c r="G180" s="5" t="inlineStr"/>
-    </row>
-    <row r="181" ht="19" customHeight="1"/>
+      <c r="G181" s="5" t="inlineStr"/>
+    </row>
     <row r="182" ht="19" customHeight="1">
       <c r="A182" s="2" t="inlineStr"/>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>AO3401A</t>
+          <t>6V/200mA</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>Fuse_0805_2012Metric</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>122.0, 93.9</t>
+          <t>98.3, 71.7</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr"/>
@@ -5663,27 +5699,27 @@
       <c r="A183" s="2" t="inlineStr"/>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>AO3401A</t>
+          <t>6V/200mA</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>Fuse_0805_2012Metric</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>95.3, 71.7</t>
+          <t>60.3, 75.9</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr"/>
@@ -5692,218 +5728,174 @@
       <c r="A184" s="2" t="inlineStr"/>
       <c r="B184" s="3" t="inlineStr">
         <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>6V/200mA</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>Fuse_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>60.3, 69.2</t>
+        </is>
+      </c>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>C 传感器 + GNSS</t>
+        </is>
+      </c>
+      <c r="G184" s="5" t="inlineStr"/>
+    </row>
+    <row r="185" ht="19" customHeight="1"/>
+    <row r="186" ht="19" customHeight="1">
+      <c r="A186" s="2" t="inlineStr"/>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>AO3401A</t>
+        </is>
+      </c>
+      <c r="D186" s="4" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>122.0, 93.9</t>
+        </is>
+      </c>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t>D 978 收发</t>
+        </is>
+      </c>
+      <c r="G186" s="5" t="inlineStr"/>
+    </row>
+    <row r="187" ht="19" customHeight="1">
+      <c r="A187" s="2" t="inlineStr"/>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>AO3401A</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>95.3, 71.7</t>
+        </is>
+      </c>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t>E 1090 接收链</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr"/>
+    </row>
+    <row r="188" ht="19" customHeight="1">
+      <c r="A188" s="2" t="inlineStr"/>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="C184" s="4" t="inlineStr">
+      <c r="C188" s="4" t="inlineStr">
         <is>
           <t>AO3401A</t>
         </is>
       </c>
-      <c r="D184" s="4" t="inlineStr">
+      <c r="D188" s="4" t="inlineStr">
         <is>
           <t>SOT-23</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>63.5, 75.9</t>
         </is>
       </c>
-      <c r="F184" s="4" t="inlineStr">
+      <c r="F188" s="4" t="inlineStr">
         <is>
           <t>C 传感器 + GNSS</t>
         </is>
       </c>
-      <c r="G184" s="5" t="inlineStr"/>
-    </row>
-    <row r="185" ht="19" customHeight="1">
-      <c r="A185" s="2" t="inlineStr"/>
-      <c r="B185" s="3" t="inlineStr">
+      <c r="G188" s="5" t="inlineStr"/>
+    </row>
+    <row r="189" ht="19" customHeight="1">
+      <c r="A189" s="2" t="inlineStr"/>
+      <c r="B189" s="3" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="C185" s="4" t="inlineStr">
+      <c r="C189" s="4" t="inlineStr">
         <is>
           <t>AO3401A</t>
         </is>
       </c>
-      <c r="D185" s="4" t="inlineStr">
+      <c r="D189" s="4" t="inlineStr">
         <is>
           <t>SOT-23</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>63.5, 69.2</t>
         </is>
       </c>
-      <c r="F185" s="4" t="inlineStr">
+      <c r="F189" s="4" t="inlineStr">
         <is>
           <t>C 传感器 + GNSS</t>
         </is>
       </c>
-      <c r="G185" s="5" t="inlineStr"/>
-    </row>
-    <row r="186" ht="19" customHeight="1"/>
-    <row r="187" ht="19" customHeight="1">
-      <c r="A187" s="10" t="inlineStr"/>
-      <c r="B187" s="11" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="C187" s="12" t="inlineStr">
-        <is>
-          <t>ME6211C33M5</t>
-        </is>
-      </c>
-      <c r="D187" s="12" t="inlineStr">
-        <is>
-          <t>SOT-23-5</t>
-        </is>
-      </c>
-      <c r="E187" s="10" t="inlineStr">
-        <is>
-          <t>74.7, 97.8</t>
-        </is>
-      </c>
-      <c r="F187" s="12" t="inlineStr">
-        <is>
-          <t>A 电源</t>
-        </is>
-      </c>
-      <c r="G187" s="13" t="inlineStr">
-        <is>
-          <t>认 pin1（缺角/圆点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="19" customHeight="1">
-      <c r="A188" s="10" t="inlineStr"/>
-      <c r="B188" s="11" t="inlineStr">
-        <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="C188" s="12" t="inlineStr">
-        <is>
-          <t>TPS7A2033PDBVR</t>
-        </is>
-      </c>
-      <c r="D188" s="12" t="inlineStr">
-        <is>
-          <t>SOT-23-5</t>
-        </is>
-      </c>
-      <c r="E188" s="10" t="inlineStr">
-        <is>
-          <t>82.3, 97.8</t>
-        </is>
-      </c>
-      <c r="F188" s="12" t="inlineStr">
-        <is>
-          <t>A 电源</t>
-        </is>
-      </c>
-      <c r="G188" s="13" t="inlineStr">
-        <is>
-          <t>认 pin1（缺角/圆点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="19" customHeight="1">
-      <c r="A189" s="10" t="inlineStr"/>
-      <c r="B189" s="11" t="inlineStr">
-        <is>
-          <t>U3</t>
-        </is>
-      </c>
-      <c r="C189" s="12" t="inlineStr">
-        <is>
-          <t>TPS7A2033PDBVR</t>
-        </is>
-      </c>
-      <c r="D189" s="12" t="inlineStr">
-        <is>
-          <t>SOT-23-5</t>
-        </is>
-      </c>
-      <c r="E189" s="10" t="inlineStr">
-        <is>
-          <t>89.2, 97.8</t>
-        </is>
-      </c>
-      <c r="F189" s="12" t="inlineStr">
-        <is>
-          <t>A 电源</t>
-        </is>
-      </c>
-      <c r="G189" s="13" t="inlineStr">
-        <is>
-          <t>认 pin1（缺角/圆点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="19" customHeight="1">
-      <c r="A190" s="10" t="inlineStr"/>
-      <c r="B190" s="11" t="inlineStr">
-        <is>
-          <t>U4</t>
-        </is>
-      </c>
-      <c r="C190" s="12" t="inlineStr">
-        <is>
-          <t>BNO085</t>
-        </is>
-      </c>
-      <c r="D190" s="12" t="inlineStr">
-        <is>
-          <t>BNO085_LGA-28</t>
-        </is>
-      </c>
-      <c r="E190" s="10" t="inlineStr">
-        <is>
-          <t>59.7, 84.5</t>
-        </is>
-      </c>
-      <c r="F190" s="12" t="inlineStr">
-        <is>
-          <t>C 传感器 + GNSS</t>
-        </is>
-      </c>
-      <c r="G190" s="13" t="inlineStr">
-        <is>
-          <t>认 pin1（缺角/圆点）</t>
-        </is>
-      </c>
-    </row>
+      <c r="G189" s="5" t="inlineStr"/>
+    </row>
+    <row r="190" ht="19" customHeight="1"/>
     <row r="191" ht="19" customHeight="1">
       <c r="A191" s="10" t="inlineStr"/>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>BMP388</t>
+          <t>ME6211C33M5</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>BMP388_LGA-10</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="E191" s="10" t="inlineStr">
         <is>
-          <t>61.0, 88.9</t>
+          <t>74.7, 97.8</t>
         </is>
       </c>
       <c r="F191" s="12" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>A 电源</t>
         </is>
       </c>
       <c r="G191" s="13" t="inlineStr">
@@ -5916,27 +5908,27 @@
       <c r="A192" s="10" t="inlineStr"/>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="C192" s="12" t="inlineStr">
         <is>
-          <t>QMC5883P</t>
+          <t>TPS7A2033PDBVR</t>
         </is>
       </c>
       <c r="D192" s="12" t="inlineStr">
         <is>
-          <t>LGA-16_3x3mm_P0.5mm</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="E192" s="10" t="inlineStr">
         <is>
-          <t>59.7, 96.5</t>
+          <t>82.3, 97.8</t>
         </is>
       </c>
       <c r="F192" s="12" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>A 电源</t>
         </is>
       </c>
       <c r="G192" s="13" t="inlineStr">
@@ -5949,27 +5941,27 @@
       <c r="A193" s="10" t="inlineStr"/>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>ATGM336H-6N-74</t>
+          <t>TPS7A2033PDBVR</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>ATGM336H_LCC-18</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="E193" s="10" t="inlineStr">
         <is>
-          <t>73.7, 89.1</t>
+          <t>89.2, 97.8</t>
         </is>
       </c>
       <c r="F193" s="12" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>A 电源</t>
         </is>
       </c>
       <c r="G193" s="13" t="inlineStr">
@@ -5982,27 +5974,27 @@
       <c r="A194" s="10" t="inlineStr"/>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="C194" s="12" t="inlineStr">
         <is>
-          <t>RP2040</t>
+          <t>BNO085</t>
         </is>
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>QFN-56-1EP_7x7mm_P0.4mm_EP3.2x3.2mm</t>
+          <t>BNO085_LGA-28</t>
         </is>
       </c>
       <c r="E194" s="10" t="inlineStr">
         <is>
-          <t>86.4, 76.9</t>
+          <t>59.7, 84.5</t>
         </is>
       </c>
       <c r="F194" s="12" t="inlineStr">
         <is>
-          <t>B MCU + Flash</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G194" s="13" t="inlineStr">
@@ -6015,27 +6007,27 @@
       <c r="A195" s="10" t="inlineStr"/>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>W25Q128JVSIQ</t>
+          <t>BMP388</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>SOIC-8_5.3x5.3mm_P1.27mm</t>
+          <t>BMP388_LGA-10</t>
         </is>
       </c>
       <c r="E195" s="10" t="inlineStr">
         <is>
-          <t>93.7, 85.9</t>
+          <t>61.0, 88.9</t>
         </is>
       </c>
       <c r="F195" s="12" t="inlineStr">
         <is>
-          <t>B MCU + Flash</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G195" s="13" t="inlineStr">
@@ -6048,27 +6040,27 @@
       <c r="A196" s="10" t="inlineStr"/>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="C196" s="12" t="inlineStr">
         <is>
-          <t>CC1312R1F3RGZR</t>
+          <t>QMC5883P</t>
         </is>
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>QFN-48-1EP_7x7mm_P0.5mm_EP5.15x5.15mm</t>
+          <t>LGA-16_3x3mm_P0.5mm</t>
         </is>
       </c>
       <c r="E196" s="10" t="inlineStr">
         <is>
-          <t>104.5, 92.0</t>
+          <t>59.7, 96.5</t>
         </is>
       </c>
       <c r="F196" s="12" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G196" s="13" t="inlineStr">
@@ -6081,27 +6073,27 @@
       <c r="A197" s="10" t="inlineStr"/>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>QPL9547TR7</t>
+          <t>ATGM336H-6N-74</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>DFN-8-1EP_2x2mm_P0.5mm_EP0.86x1.55mm</t>
+          <t>ATGM336H_LCC-18</t>
         </is>
       </c>
       <c r="E197" s="10" t="inlineStr">
         <is>
-          <t>107.7, 61.9</t>
+          <t>73.7, 89.1</t>
         </is>
       </c>
       <c r="F197" s="12" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G197" s="13" t="inlineStr">
@@ -6114,27 +6106,27 @@
       <c r="A198" s="10" t="inlineStr"/>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="C198" s="12" t="inlineStr">
         <is>
-          <t>BGA2817</t>
+          <t>RP2040</t>
         </is>
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>SOT-363_SC-70-6</t>
+          <t>QFN-56-1EP_7x7mm_P0.4mm_EP3.2x3.2mm</t>
         </is>
       </c>
       <c r="E198" s="10" t="inlineStr">
         <is>
-          <t>117.1, 62.5</t>
+          <t>86.4, 76.9</t>
         </is>
       </c>
       <c r="F198" s="12" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>B MCU + Flash</t>
         </is>
       </c>
       <c r="G198" s="13" t="inlineStr">
@@ -6147,27 +6139,27 @@
       <c r="A199" s="10" t="inlineStr"/>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>AD8313ARMZ</t>
+          <t>W25Q128JVSIQ</t>
         </is>
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>MSOP-8_3x3mm_P0.65mm</t>
+          <t>SOIC-8_5.3x5.3mm_P1.27mm</t>
         </is>
       </c>
       <c r="E199" s="10" t="inlineStr">
         <is>
-          <t>111.1, 73.4</t>
+          <t>93.7, 85.9</t>
         </is>
       </c>
       <c r="F199" s="12" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>B MCU + Flash</t>
         </is>
       </c>
       <c r="G199" s="13" t="inlineStr">
@@ -6180,27 +6172,27 @@
       <c r="A200" s="10" t="inlineStr"/>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>U15</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="C200" s="12" t="inlineStr">
         <is>
-          <t>TLV3501(TOKMAS)</t>
+          <t>CC1312R1F3RGZR</t>
         </is>
       </c>
       <c r="D200" s="12" t="inlineStr">
         <is>
-          <t>SOT-23-6</t>
+          <t>QFN-48-1EP_7x7mm_P0.5mm_EP5.15x5.15mm</t>
         </is>
       </c>
       <c r="E200" s="10" t="inlineStr">
         <is>
-          <t>100.6, 79.5</t>
+          <t>104.5, 92.0</t>
         </is>
       </c>
       <c r="F200" s="12" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>D 978 收发</t>
         </is>
       </c>
       <c r="G200" s="13" t="inlineStr">
@@ -6213,22 +6205,22 @@
       <c r="A201" s="10" t="inlineStr"/>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>XA17-G4K</t>
+          <t>QPL9547TR7</t>
         </is>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>SOT-363_SC-70-6</t>
+          <t>DFN-8-1EP_2x2mm_P0.5mm_EP0.86x1.55mm</t>
         </is>
       </c>
       <c r="E201" s="10" t="inlineStr">
         <is>
-          <t>98.0, 62.9</t>
+          <t>107.7, 61.9</t>
         </is>
       </c>
       <c r="F201" s="12" t="inlineStr">
@@ -6246,12 +6238,12 @@
       <c r="A202" s="10" t="inlineStr"/>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>U17</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="C202" s="12" t="inlineStr">
         <is>
-          <t>XA17-G4K</t>
+          <t>BGA2817</t>
         </is>
       </c>
       <c r="D202" s="12" t="inlineStr">
@@ -6261,12 +6253,12 @@
       </c>
       <c r="E202" s="10" t="inlineStr">
         <is>
-          <t>68.6, 78.1</t>
+          <t>117.1, 62.5</t>
         </is>
       </c>
       <c r="F202" s="12" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G202" s="13" t="inlineStr">
@@ -6279,27 +6271,27 @@
       <c r="A203" s="10" t="inlineStr"/>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C203" s="12" t="inlineStr">
         <is>
-          <t>CH224K</t>
+          <t>AD8313ARMZ</t>
         </is>
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>CH224K_ESSOP-10</t>
+          <t>MSOP-8_3x3mm_P0.65mm</t>
         </is>
       </c>
       <c r="E203" s="10" t="inlineStr">
         <is>
-          <t>132.5, 68.6</t>
+          <t>111.1, 73.4</t>
         </is>
       </c>
       <c r="F203" s="12" t="inlineStr">
         <is>
-          <t>A 电源</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G203" s="13" t="inlineStr">
@@ -6312,27 +6304,27 @@
       <c r="A204" s="10" t="inlineStr"/>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>U19</t>
+          <t>U15</t>
         </is>
       </c>
       <c r="C204" s="12" t="inlineStr">
         <is>
-          <t>SY6970</t>
+          <t>TLV3501(TOKMAS)</t>
         </is>
       </c>
       <c r="D204" s="12" t="inlineStr">
         <is>
-          <t>QFN-24-1EP_4x4mm_P0.5mm_EP2.6x2.6mm_ThermalVias</t>
+          <t>SOT-23-6</t>
         </is>
       </c>
       <c r="E204" s="10" t="inlineStr">
         <is>
-          <t>134.5, 83.7</t>
+          <t>100.6, 79.5</t>
         </is>
       </c>
       <c r="F204" s="12" t="inlineStr">
         <is>
-          <t>A 电源</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G204" s="13" t="inlineStr">
@@ -6345,27 +6337,27 @@
       <c r="A205" s="10" t="inlineStr"/>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>U20</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>SY7069</t>
+          <t>XA17-G4K</t>
         </is>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>TSOT-23-6</t>
+          <t>SOT-363_SC-70-6</t>
         </is>
       </c>
       <c r="E205" s="10" t="inlineStr">
         <is>
-          <t>139.2, 95.0</t>
+          <t>98.0, 62.9</t>
         </is>
       </c>
       <c r="F205" s="12" t="inlineStr">
         <is>
-          <t>A 电源</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G205" s="13" t="inlineStr">
@@ -6378,27 +6370,27 @@
       <c r="A206" s="10" t="inlineStr"/>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>U21</t>
+          <t>U17</t>
         </is>
       </c>
       <c r="C206" s="12" t="inlineStr">
         <is>
-          <t>BK4819QN32SC</t>
+          <t>XA17-G4K</t>
         </is>
       </c>
       <c r="D206" s="12" t="inlineStr">
         <is>
-          <t>QFN-32-1EP_4x4mm_P0.4mm_EP2.65x2.65mm</t>
+          <t>SOT-363_SC-70-6</t>
         </is>
       </c>
       <c r="E206" s="10" t="inlineStr">
         <is>
-          <t>127.5, 97.6</t>
+          <t>68.6, 78.1</t>
         </is>
       </c>
       <c r="F206" s="12" t="inlineStr">
         <is>
-          <t>G 航空波段 AIRBAND</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G206" s="13" t="inlineStr">
@@ -6411,27 +6403,27 @@
       <c r="A207" s="10" t="inlineStr"/>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>U22</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>PCM1808PWR</t>
+          <t>CH224K</t>
         </is>
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>TSSOP-14_4.4x5mm_P0.65mm</t>
+          <t>CH224K_ESSOP-10</t>
         </is>
       </c>
       <c r="E207" s="10" t="inlineStr">
         <is>
-          <t>122.8, 105.3</t>
+          <t>132.5, 68.6</t>
         </is>
       </c>
       <c r="F207" s="12" t="inlineStr">
         <is>
-          <t>G 航空波段 AIRBAND</t>
+          <t>A 电源</t>
         </is>
       </c>
       <c r="G207" s="13" t="inlineStr">
@@ -6444,22 +6436,22 @@
       <c r="A208" s="10" t="inlineStr"/>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>U23</t>
+          <t>U19</t>
         </is>
       </c>
       <c r="C208" s="12" t="inlineStr">
         <is>
-          <t>TPS7A2033PDBVR</t>
+          <t>SY6970</t>
         </is>
       </c>
       <c r="D208" s="12" t="inlineStr">
         <is>
-          <t>SOT-23-5</t>
+          <t>QFN-24-1EP_4x4mm_P0.5mm_EP2.6x2.6mm_ThermalVias</t>
         </is>
       </c>
       <c r="E208" s="10" t="inlineStr">
         <is>
-          <t>81.9, 93.5</t>
+          <t>134.5, 83.7</t>
         </is>
       </c>
       <c r="F208" s="12" t="inlineStr">
@@ -6473,37 +6465,69 @@
         </is>
       </c>
     </row>
-    <row r="209" ht="19" customHeight="1"/>
+    <row r="209" ht="19" customHeight="1">
+      <c r="A209" s="10" t="inlineStr"/>
+      <c r="B209" s="11" t="inlineStr">
+        <is>
+          <t>U20</t>
+        </is>
+      </c>
+      <c r="C209" s="12" t="inlineStr">
+        <is>
+          <t>SY7069</t>
+        </is>
+      </c>
+      <c r="D209" s="12" t="inlineStr">
+        <is>
+          <t>TSOT-23-6</t>
+        </is>
+      </c>
+      <c r="E209" s="10" t="inlineStr">
+        <is>
+          <t>139.2, 95.0</t>
+        </is>
+      </c>
+      <c r="F209" s="12" t="inlineStr">
+        <is>
+          <t>A 电源</t>
+        </is>
+      </c>
+      <c r="G209" s="13" t="inlineStr">
+        <is>
+          <t>认 pin1（缺角/圆点）</t>
+        </is>
+      </c>
+    </row>
     <row r="210" ht="19" customHeight="1">
       <c r="A210" s="10" t="inlineStr"/>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>FL1</t>
+          <t>U21</t>
         </is>
       </c>
       <c r="C210" s="12" t="inlineStr">
         <is>
-          <t>TA0970A</t>
+          <t>BK4819QN32SC</t>
         </is>
       </c>
       <c r="D210" s="12" t="inlineStr">
         <is>
-          <t>TA0970A_SMD3838-6</t>
+          <t>QFN-32-1EP_4x4mm_P0.4mm_EP2.65x2.65mm</t>
         </is>
       </c>
       <c r="E210" s="10" t="inlineStr">
         <is>
-          <t>112.0, 65.5</t>
+          <t>127.5, 97.6</t>
         </is>
       </c>
       <c r="F210" s="12" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>G 航空波段 AIRBAND</t>
         </is>
       </c>
       <c r="G210" s="13" t="inlineStr">
         <is>
-          <t>SAW 滤波器分输入输出，贴反不工作</t>
+          <t>认 pin1（缺角/圆点）</t>
         </is>
       </c>
     </row>
@@ -6511,306 +6535,290 @@
       <c r="A211" s="10" t="inlineStr"/>
       <c r="B211" s="11" t="inlineStr">
         <is>
+          <t>U22</t>
+        </is>
+      </c>
+      <c r="C211" s="12" t="inlineStr">
+        <is>
+          <t>PCM1808PWR</t>
+        </is>
+      </c>
+      <c r="D211" s="12" t="inlineStr">
+        <is>
+          <t>TSSOP-14_4.4x5mm_P0.65mm</t>
+        </is>
+      </c>
+      <c r="E211" s="10" t="inlineStr">
+        <is>
+          <t>122.8, 105.3</t>
+        </is>
+      </c>
+      <c r="F211" s="12" t="inlineStr">
+        <is>
+          <t>G 航空波段 AIRBAND</t>
+        </is>
+      </c>
+      <c r="G211" s="13" t="inlineStr">
+        <is>
+          <t>认 pin1（缺角/圆点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="19" customHeight="1">
+      <c r="A212" s="10" t="inlineStr"/>
+      <c r="B212" s="11" t="inlineStr">
+        <is>
+          <t>U23</t>
+        </is>
+      </c>
+      <c r="C212" s="12" t="inlineStr">
+        <is>
+          <t>TPS7A2033PDBVR</t>
+        </is>
+      </c>
+      <c r="D212" s="12" t="inlineStr">
+        <is>
+          <t>SOT-23-5</t>
+        </is>
+      </c>
+      <c r="E212" s="10" t="inlineStr">
+        <is>
+          <t>81.9, 93.5</t>
+        </is>
+      </c>
+      <c r="F212" s="12" t="inlineStr">
+        <is>
+          <t>A 电源</t>
+        </is>
+      </c>
+      <c r="G212" s="13" t="inlineStr">
+        <is>
+          <t>认 pin1（缺角/圆点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="19" customHeight="1"/>
+    <row r="214" ht="19" customHeight="1">
+      <c r="A214" s="10" t="inlineStr"/>
+      <c r="B214" s="11" t="inlineStr">
+        <is>
+          <t>FL1</t>
+        </is>
+      </c>
+      <c r="C214" s="12" t="inlineStr">
+        <is>
+          <t>TA0970A</t>
+        </is>
+      </c>
+      <c r="D214" s="12" t="inlineStr">
+        <is>
+          <t>TA0970A_SMD3838-6</t>
+        </is>
+      </c>
+      <c r="E214" s="10" t="inlineStr">
+        <is>
+          <t>112.0, 65.5</t>
+        </is>
+      </c>
+      <c r="F214" s="12" t="inlineStr">
+        <is>
+          <t>E 1090 接收链</t>
+        </is>
+      </c>
+      <c r="G214" s="13" t="inlineStr">
+        <is>
+          <t>SAW 滤波器分输入输出，贴反不工作</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="19" customHeight="1">
+      <c r="A215" s="10" t="inlineStr"/>
+      <c r="B215" s="11" t="inlineStr">
+        <is>
           <t>FL2</t>
         </is>
       </c>
-      <c r="C211" s="12" t="inlineStr">
+      <c r="C215" s="12" t="inlineStr">
         <is>
           <t>TA0970A</t>
         </is>
       </c>
-      <c r="D211" s="12" t="inlineStr">
+      <c r="D215" s="12" t="inlineStr">
         <is>
           <t>TA0970A_SMD3838-6</t>
         </is>
       </c>
-      <c r="E211" s="10" t="inlineStr">
+      <c r="E215" s="10" t="inlineStr">
         <is>
           <t>118.4, 66.5</t>
         </is>
       </c>
-      <c r="F211" s="12" t="inlineStr">
+      <c r="F215" s="12" t="inlineStr">
         <is>
           <t>E 1090 接收链</t>
         </is>
       </c>
-      <c r="G211" s="13" t="inlineStr">
+      <c r="G215" s="13" t="inlineStr">
         <is>
           <t>SAW 滤波器分输入输出，贴反不工作</t>
         </is>
       </c>
     </row>
-    <row r="212" ht="19" customHeight="1"/>
-    <row r="213" ht="19" customHeight="1">
-      <c r="A213" s="2" t="inlineStr"/>
-      <c r="B213" s="3" t="inlineStr">
+    <row r="216" ht="19" customHeight="1"/>
+    <row r="217" ht="19" customHeight="1">
+      <c r="A217" s="2" t="inlineStr"/>
+      <c r="B217" s="3" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="C213" s="4" t="inlineStr">
+      <c r="C217" s="4" t="inlineStr">
         <is>
           <t>12MHz CL=10pF ABM8-272-T3</t>
         </is>
       </c>
-      <c r="D213" s="4" t="inlineStr">
+      <c r="D217" s="4" t="inlineStr">
         <is>
           <t>Crystal_SMD_3225-4Pin_3.2x2.5mm</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>85.1, 69.1</t>
         </is>
       </c>
-      <c r="F213" s="4" t="inlineStr">
+      <c r="F217" s="4" t="inlineStr">
         <is>
           <t>B MCU + Flash</t>
         </is>
       </c>
-      <c r="G213" s="5" t="inlineStr">
+      <c r="G217" s="5" t="inlineStr">
         <is>
           <t>无源晶体，转 180° 等价，长边对长边即可</t>
         </is>
       </c>
     </row>
-    <row r="214" ht="19" customHeight="1">
-      <c r="A214" s="2" t="inlineStr"/>
-      <c r="B214" s="3" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="C214" s="4" t="inlineStr">
-        <is>
-          <t>48MHz ABM8W-7pF</t>
-        </is>
-      </c>
-      <c r="D214" s="4" t="inlineStr">
-        <is>
-          <t>Crystal_SMD_3225-4Pin_3.2x2.5mm</t>
-        </is>
-      </c>
-      <c r="E214" s="2" t="inlineStr">
-        <is>
-          <t>108.3, 98.3</t>
-        </is>
-      </c>
-      <c r="F214" s="4" t="inlineStr">
-        <is>
-          <t>D 978 收发</t>
-        </is>
-      </c>
-      <c r="G214" s="5" t="inlineStr">
-        <is>
-          <t>无源晶体，转 180° 等价，长边对长边即可</t>
-        </is>
-      </c>
-    </row>
-    <row r="215" ht="19" customHeight="1">
-      <c r="A215" s="2" t="inlineStr"/>
-      <c r="B215" s="3" t="inlineStr">
-        <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="C215" s="4" t="inlineStr">
-        <is>
-          <t>32.768kHz FC-135</t>
-        </is>
-      </c>
-      <c r="D215" s="4" t="inlineStr">
-        <is>
-          <t>Crystal_SMD_3215-2Pin_3.2x1.5mm</t>
-        </is>
-      </c>
-      <c r="E215" s="2" t="inlineStr">
-        <is>
-          <t>111.6, 87.0</t>
-        </is>
-      </c>
-      <c r="F215" s="4" t="inlineStr">
-        <is>
-          <t>D 978 收发</t>
-        </is>
-      </c>
-      <c r="G215" s="5" t="inlineStr"/>
-    </row>
-    <row r="216" ht="19" customHeight="1">
-      <c r="A216" s="10" t="inlineStr"/>
-      <c r="B216" s="11" t="inlineStr">
-        <is>
-          <t>Y4</t>
-        </is>
-      </c>
-      <c r="C216" s="12" t="inlineStr">
-        <is>
-          <t>26MHz TCXO &lt;=2.5ppm</t>
-        </is>
-      </c>
-      <c r="D216" s="12" t="inlineStr">
-        <is>
-          <t>Crystal_SMD_2520-4Pin_2.5x2.0mm</t>
-        </is>
-      </c>
-      <c r="E216" s="10" t="inlineStr">
-        <is>
-          <t>135.1, 102.5</t>
-        </is>
-      </c>
-      <c r="F216" s="12" t="inlineStr">
-        <is>
-          <t>G 航空波段 AIRBAND</t>
-        </is>
-      </c>
-      <c r="G216" s="13" t="inlineStr">
-        <is>
-          <t>有源 TCXO：pin2=GND / pin4=Vcc，转 180° 直接短路、上电即烧。顶面无标记，倒角在底面 #1 角（手册 C0.2）——贴前翻过来认，或先用一颗定出「底面倒角↔顶面打标」的对应关系再批量贴；板上丝印的实心圆点指向 pin1</t>
-        </is>
-      </c>
-    </row>
-    <row r="217" ht="19" customHeight="1"/>
     <row r="218" ht="19" customHeight="1">
       <c r="A218" s="2" t="inlineStr"/>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>Y2</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>J3_HAT_2x20_SMD排针</t>
+          <t>48MHz ABM8W-7pF</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>PinHeader_2x20_P2.54mm_Vertical_SMD</t>
+          <t>Crystal_SMD_3225-4Pin_3.2x2.5mm</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>92.6, 106.3</t>
+          <t>108.3, 98.3</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>F 对外接口</t>
-        </is>
-      </c>
-      <c r="G218" s="5" t="inlineStr"/>
+          <t>D 978 收发</t>
+        </is>
+      </c>
+      <c r="G218" s="5" t="inlineStr">
+        <is>
+          <t>无源晶体，转 180° 等价，长边对长边即可</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="19" customHeight="1">
       <c r="A219" s="2" t="inlineStr"/>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>Y3</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>U.FL_GNSS_EXT(经尾线转SMA)</t>
+          <t>32.768kHz FC-135</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>U.FL_Hirose_U.FL-R-SMT-1_Vertical</t>
+          <t>Crystal_SMD_3215-2Pin_3.2x1.5mm</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>54.0, 75.9</t>
+          <t>111.6, 87.0</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>D 978 收发</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr"/>
     </row>
     <row r="220" ht="19" customHeight="1">
-      <c r="A220" s="2" t="inlineStr"/>
-      <c r="B220" s="3" t="inlineStr">
-        <is>
-          <t>J4</t>
-        </is>
-      </c>
-      <c r="C220" s="4" t="inlineStr">
-        <is>
-          <t>USB-C_16P</t>
-        </is>
-      </c>
-      <c r="D220" s="4" t="inlineStr">
-        <is>
-          <t>USB_C_Receptacle_HRO_TYPE-C-31-M-12</t>
-        </is>
-      </c>
-      <c r="E220" s="2" t="inlineStr">
-        <is>
-          <t>145.8, 73.0</t>
-        </is>
-      </c>
-      <c r="F220" s="4" t="inlineStr">
-        <is>
-          <t>B MCU + Flash</t>
-        </is>
-      </c>
-      <c r="G220" s="5" t="inlineStr"/>
-    </row>
-    <row r="221" ht="19" customHeight="1">
-      <c r="A221" s="2" t="inlineStr"/>
-      <c r="B221" s="3" t="inlineStr">
-        <is>
-          <t>J5</t>
-        </is>
-      </c>
-      <c r="C221" s="4" t="inlineStr">
-        <is>
-          <t>U.FL_978</t>
-        </is>
-      </c>
-      <c r="D221" s="4" t="inlineStr">
-        <is>
-          <t>U.FL_Hirose_U.FL-R-SMT-1_Vertical</t>
-        </is>
-      </c>
-      <c r="E221" s="2" t="inlineStr">
-        <is>
-          <t>118.3, 82.9</t>
-        </is>
-      </c>
-      <c r="F221" s="4" t="inlineStr">
-        <is>
-          <t>D 978 收发</t>
-        </is>
-      </c>
-      <c r="G221" s="5" t="inlineStr"/>
-    </row>
+      <c r="A220" s="10" t="inlineStr"/>
+      <c r="B220" s="11" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="C220" s="12" t="inlineStr">
+        <is>
+          <t>26MHz TCXO &lt;=2.5ppm</t>
+        </is>
+      </c>
+      <c r="D220" s="12" t="inlineStr">
+        <is>
+          <t>Crystal_SMD_2520-4Pin_2.5x2.0mm</t>
+        </is>
+      </c>
+      <c r="E220" s="10" t="inlineStr">
+        <is>
+          <t>135.1, 102.5</t>
+        </is>
+      </c>
+      <c r="F220" s="12" t="inlineStr">
+        <is>
+          <t>G 航空波段 AIRBAND</t>
+        </is>
+      </c>
+      <c r="G220" s="13" t="inlineStr">
+        <is>
+          <t>有源 TCXO：pin2=GND / pin4=Vcc，转 180° 直接短路、上电即烧。顶面无标记，倒角在底面 #1 角（手册 C0.2）——贴前翻过来认，或先用一颗定出「底面倒角↔顶面打标」的对应关系再批量贴；板上丝印的实心圆点指向 pin1</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="19" customHeight="1"/>
     <row r="222" ht="19" customHeight="1">
       <c r="A222" s="2" t="inlineStr"/>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>J6</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>U.FL_1090_EXT(经尾线转SMA)</t>
+          <t>J3_HAT_2x20_SMD排针</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>U.FL_Hirose_U.FL-R-SMT-1_Vertical</t>
+          <t>PinHeader_2x20_P2.54mm_Vertical_SMD</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>106.5, 67.3</t>
+          <t>92.6, 106.3</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>F 对外接口</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr"/>
@@ -6819,12 +6827,12 @@
       <c r="A223" s="2" t="inlineStr"/>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>J7</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>U.FL_IFA_TEST(π后调试口)</t>
+          <t>U.FL_GNSS_EXT(经尾线转SMA)</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
@@ -6834,12 +6842,12 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>90.0, 61.3</t>
+          <t>54.0, 75.9</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr"/>
@@ -6848,27 +6856,27 @@
       <c r="A224" s="2" t="inlineStr"/>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>J8</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>U.FL→内置patch</t>
+          <t>USB-C_16P</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>U.FL_Hirose_U.FL-R-SMT-1_Vertical</t>
+          <t>USB_C_Receptacle_HRO_TYPE-C-31-M-12</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>54.0, 69.2</t>
+          <t>145.8, 73.0</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>B MCU + Flash</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr"/>
@@ -6877,27 +6885,27 @@
       <c r="A225" s="2" t="inlineStr"/>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>J9</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>MX1.25WT-2P BAT</t>
+          <t>U.FL_978</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>MX1.25WT-2P_1x02-1MP_P1.25mm_Horizontal</t>
+          <t>U.FL_Hirose_U.FL-R-SMT-1_Vertical</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>144.8, 99.0</t>
+          <t>118.3, 82.9</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>A 电源</t>
+          <t>D 978 收发</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr"/>
@@ -6906,280 +6914,308 @@
       <c r="A226" s="2" t="inlineStr"/>
       <c r="B226" s="3" t="inlineStr">
         <is>
+          <t>J6</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>U.FL_1090_EXT(经尾线转SMA)</t>
+        </is>
+      </c>
+      <c r="D226" s="4" t="inlineStr">
+        <is>
+          <t>U.FL_Hirose_U.FL-R-SMT-1_Vertical</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>106.5, 67.3</t>
+        </is>
+      </c>
+      <c r="F226" s="4" t="inlineStr">
+        <is>
+          <t>E 1090 接收链</t>
+        </is>
+      </c>
+      <c r="G226" s="5" t="inlineStr"/>
+    </row>
+    <row r="227" ht="19" customHeight="1">
+      <c r="A227" s="2" t="inlineStr"/>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>J7</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="inlineStr">
+        <is>
+          <t>U.FL_IFA_TEST(π后调试口)</t>
+        </is>
+      </c>
+      <c r="D227" s="4" t="inlineStr">
+        <is>
+          <t>U.FL_Hirose_U.FL-R-SMT-1_Vertical</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>90.0, 61.3</t>
+        </is>
+      </c>
+      <c r="F227" s="4" t="inlineStr">
+        <is>
+          <t>E 1090 接收链</t>
+        </is>
+      </c>
+      <c r="G227" s="5" t="inlineStr"/>
+    </row>
+    <row r="228" ht="19" customHeight="1">
+      <c r="A228" s="2" t="inlineStr"/>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>J8</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>U.FL→内置patch</t>
+        </is>
+      </c>
+      <c r="D228" s="4" t="inlineStr">
+        <is>
+          <t>U.FL_Hirose_U.FL-R-SMT-1_Vertical</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>54.0, 69.2</t>
+        </is>
+      </c>
+      <c r="F228" s="4" t="inlineStr">
+        <is>
+          <t>C 传感器 + GNSS</t>
+        </is>
+      </c>
+      <c r="G228" s="5" t="inlineStr"/>
+    </row>
+    <row r="229" ht="19" customHeight="1">
+      <c r="A229" s="2" t="inlineStr"/>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>J9</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>MX1.25WT-2P BAT</t>
+        </is>
+      </c>
+      <c r="D229" s="4" t="inlineStr">
+        <is>
+          <t>MX1.25WT-2P_1x02-1MP_P1.25mm_Horizontal</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>144.8, 99.0</t>
+        </is>
+      </c>
+      <c r="F229" s="4" t="inlineStr">
+        <is>
+          <t>A 电源</t>
+        </is>
+      </c>
+      <c r="G229" s="5" t="inlineStr"/>
+    </row>
+    <row r="230" ht="19" customHeight="1">
+      <c r="A230" s="2" t="inlineStr"/>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
           <t>J10</t>
         </is>
       </c>
-      <c r="C226" s="4" t="inlineStr">
+      <c r="C230" s="4" t="inlineStr">
         <is>
           <t>U.FL_VHF(经尾线转SMA)</t>
         </is>
       </c>
-      <c r="D226" s="4" t="inlineStr">
+      <c r="D230" s="4" t="inlineStr">
         <is>
           <t>U.FL_Hirose_U.FL-R-SMT-1_Vertical</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="E230" s="2" t="inlineStr">
         <is>
           <t>124.4, 82.9</t>
         </is>
       </c>
-      <c r="F226" s="4" t="inlineStr">
+      <c r="F230" s="4" t="inlineStr">
         <is>
           <t>G 航空波段 AIRBAND</t>
         </is>
       </c>
-      <c r="G226" s="5" t="inlineStr"/>
-    </row>
-    <row r="227" ht="19" customHeight="1"/>
-    <row r="228" ht="19" customHeight="1">
-      <c r="A228" s="6" t="inlineStr"/>
-      <c r="B228" s="7" t="inlineStr">
+      <c r="G230" s="5" t="inlineStr"/>
+    </row>
+    <row r="231" ht="19" customHeight="1"/>
+    <row r="232" ht="19" customHeight="1">
+      <c r="A232" s="6" t="inlineStr"/>
+      <c r="B232" s="7" t="inlineStr">
         <is>
           <t>ANT1</t>
         </is>
       </c>
-      <c r="C228" s="8" t="inlineStr">
+      <c r="C232" s="8" t="inlineStr">
         <is>
           <t>IFA_1090</t>
         </is>
       </c>
-      <c r="D228" s="8" t="inlineStr">
+      <c r="D232" s="8" t="inlineStr">
         <is>
           <t>ANT_IFA_1090MHz</t>
         </is>
       </c>
-      <c r="E228" s="6" t="inlineStr">
+      <c r="E232" s="6" t="inlineStr">
         <is>
           <t>79.2, 57.8</t>
         </is>
       </c>
-      <c r="F228" s="8" t="inlineStr">
+      <c r="F232" s="8" t="inlineStr">
         <is>
           <t>不贴（板载天线）</t>
         </is>
       </c>
-      <c r="G228" s="9" t="inlineStr">
+      <c r="G232" s="9" t="inlineStr">
         <is>
           <t>50.0mm外包络/48.5mm中心线；V4.0装盒实测1082.5MHz、SWR 1.09</t>
         </is>
       </c>
     </row>
-    <row r="229" ht="19" customHeight="1"/>
-    <row r="230" ht="19" customHeight="1">
-      <c r="A230" s="6" t="inlineStr"/>
-      <c r="B230" s="7" t="inlineStr">
+    <row r="233" ht="19" customHeight="1"/>
+    <row r="234" ht="19" customHeight="1">
+      <c r="A234" s="6" t="inlineStr"/>
+      <c r="B234" s="7" t="inlineStr">
         <is>
           <t>ZP1</t>
         </is>
       </c>
-      <c r="C230" s="8" t="inlineStr">
+      <c r="C234" s="8" t="inlineStr">
         <is>
           <t>DNP 并-天线侧</t>
         </is>
       </c>
-      <c r="D230" s="8" t="inlineStr">
+      <c r="D234" s="8" t="inlineStr">
         <is>
           <t>C_0603_1608Metric</t>
         </is>
       </c>
-      <c r="E230" s="6" t="inlineStr">
+      <c r="E234" s="6" t="inlineStr">
         <is>
           <t>79.2, 63.6</t>
         </is>
       </c>
-      <c r="F230" s="8" t="inlineStr">
+      <c r="F234" s="8" t="inlineStr">
         <is>
           <t>不贴（DNP）</t>
         </is>
       </c>
-      <c r="G230" s="9" t="inlineStr">
+      <c r="G234" s="9" t="inlineStr">
         <is>
           <t>默认DNP；V4.0实测直通状态</t>
         </is>
       </c>
     </row>
-    <row r="231" ht="19" customHeight="1">
-      <c r="A231" s="6" t="inlineStr"/>
-      <c r="B231" s="7" t="inlineStr">
-        <is>
-          <t>ZP2</t>
-        </is>
-      </c>
-      <c r="C231" s="8" t="inlineStr">
-        <is>
-          <t>DNP 并-电台侧</t>
-        </is>
-      </c>
-      <c r="D231" s="8" t="inlineStr">
-        <is>
-          <t>C_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="E231" s="6" t="inlineStr">
-        <is>
-          <t>84.2, 63.6</t>
-        </is>
-      </c>
-      <c r="F231" s="8" t="inlineStr">
-        <is>
-          <t>不贴（DNP）</t>
-        </is>
-      </c>
-      <c r="G231" s="9" t="inlineStr">
-        <is>
-          <t>默认DNP；历史HFSS 3.3pF仅作异常复调备选</t>
-        </is>
-      </c>
-    </row>
-    <row r="232" ht="19" customHeight="1"/>
-    <row r="233" ht="19" customHeight="1">
-      <c r="A233" s="2" t="inlineStr"/>
-      <c r="B233" s="3" t="inlineStr">
-        <is>
-          <t>ZS1</t>
-        </is>
-      </c>
-      <c r="C233" s="4" t="inlineStr">
-        <is>
-          <t>0R 串</t>
-        </is>
-      </c>
-      <c r="D233" s="4" t="inlineStr">
-        <is>
-          <t>L_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="E233" s="2" t="inlineStr">
-        <is>
-          <t>81.7, 62.9</t>
-        </is>
-      </c>
-      <c r="F233" s="4" t="inlineStr">
-        <is>
-          <t>E 1090 接收链</t>
-        </is>
-      </c>
-      <c r="G233" s="5" t="inlineStr">
-        <is>
-          <t>默认0R直通；V4.0实测即为此状态</t>
-        </is>
-      </c>
-    </row>
-    <row r="234" ht="19" customHeight="1"/>
     <row r="235" ht="19" customHeight="1">
       <c r="A235" s="6" t="inlineStr"/>
       <c r="B235" s="7" t="inlineStr">
         <is>
-          <t>SW1</t>
+          <t>ZP2</t>
         </is>
       </c>
       <c r="C235" s="8" t="inlineStr">
         <is>
-          <t>RESET短接焊盘</t>
+          <t>DNP 并-电台侧</t>
         </is>
       </c>
       <c r="D235" s="8" t="inlineStr">
         <is>
-          <t>SolderJumper-2_P1.3mm_Open_Pad1.0x1.5mm</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="E235" s="6" t="inlineStr">
         <is>
-          <t>51.9, 77.5</t>
+          <t>84.2, 63.6</t>
         </is>
       </c>
       <c r="F235" s="8" t="inlineStr">
         <is>
-          <t>不贴（短接焊盘）</t>
-        </is>
-      </c>
-      <c r="G235" s="9" t="inlineStr"/>
-    </row>
-    <row r="236" ht="19" customHeight="1">
-      <c r="A236" s="6" t="inlineStr"/>
-      <c r="B236" s="7" t="inlineStr">
-        <is>
-          <t>SW2</t>
-        </is>
-      </c>
-      <c r="C236" s="8" t="inlineStr">
-        <is>
-          <t>BOOTSEL短接焊盘</t>
-        </is>
-      </c>
-      <c r="D236" s="8" t="inlineStr">
-        <is>
-          <t>SolderJumper-2_P1.3mm_Open_Pad1.0x1.5mm</t>
-        </is>
-      </c>
-      <c r="E236" s="6" t="inlineStr">
-        <is>
-          <t>51.9, 81.0</t>
-        </is>
-      </c>
-      <c r="F236" s="8" t="inlineStr">
-        <is>
-          <t>不贴（短接焊盘）</t>
-        </is>
-      </c>
-      <c r="G236" s="9" t="inlineStr"/>
-    </row>
+          <t>不贴（DNP）</t>
+        </is>
+      </c>
+      <c r="G235" s="9" t="inlineStr">
+        <is>
+          <t>默认DNP；历史HFSS 3.3pF仅作异常复调备选</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="19" customHeight="1"/>
     <row r="237" ht="19" customHeight="1">
       <c r="A237" s="2" t="inlineStr"/>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>SW3</t>
+          <t>ZS1</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>TS24CA</t>
+          <t>0R 串</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>SW_TS24CA_2x4_SideAct</t>
+          <t>L_0603_1608Metric</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>147.9, 89.1</t>
+          <t>81.7, 62.9</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>A 电源</t>
-        </is>
-      </c>
-      <c r="G237" s="5" t="inlineStr"/>
+          <t>E 1090 接收链</t>
+        </is>
+      </c>
+      <c r="G237" s="5" t="inlineStr">
+        <is>
+          <t>默认0R直通；V4.0实测即为此状态</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="19" customHeight="1"/>
     <row r="239" ht="19" customHeight="1">
       <c r="A239" s="6" t="inlineStr"/>
       <c r="B239" s="7" t="inlineStr">
         <is>
-          <t>TP1</t>
+          <t>SW1</t>
         </is>
       </c>
       <c r="C239" s="8" t="inlineStr">
         <is>
-          <t>TestPoint</t>
+          <t>RESET短接焊盘</t>
         </is>
       </c>
       <c r="D239" s="8" t="inlineStr">
         <is>
-          <t>TestPoint_Pad_1.0x1.0mm</t>
+          <t>SolderJumper-2_P1.3mm_Open_Pad1.0x1.5mm</t>
         </is>
       </c>
       <c r="E239" s="6" t="inlineStr">
         <is>
-          <t>51.9, 86.0</t>
+          <t>51.9, 77.5</t>
         </is>
       </c>
       <c r="F239" s="8" t="inlineStr">
         <is>
-          <t>不贴（测试点焊盘）</t>
+          <t>不贴（短接焊盘）</t>
         </is>
       </c>
       <c r="G239" s="9" t="inlineStr"/>
@@ -7188,94 +7224,66 @@
       <c r="A240" s="6" t="inlineStr"/>
       <c r="B240" s="7" t="inlineStr">
         <is>
-          <t>TP2</t>
+          <t>SW2</t>
         </is>
       </c>
       <c r="C240" s="8" t="inlineStr">
         <is>
-          <t>TestPoint</t>
+          <t>BOOTSEL短接焊盘</t>
         </is>
       </c>
       <c r="D240" s="8" t="inlineStr">
         <is>
-          <t>TestPoint_Pad_1.0x1.0mm</t>
+          <t>SolderJumper-2_P1.3mm_Open_Pad1.0x1.5mm</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
         <is>
-          <t>51.9, 88.1</t>
+          <t>51.9, 81.0</t>
         </is>
       </c>
       <c r="F240" s="8" t="inlineStr">
         <is>
-          <t>不贴（测试点焊盘）</t>
+          <t>不贴（短接焊盘）</t>
         </is>
       </c>
       <c r="G240" s="9" t="inlineStr"/>
     </row>
     <row r="241" ht="19" customHeight="1">
-      <c r="A241" s="6" t="inlineStr"/>
-      <c r="B241" s="7" t="inlineStr">
-        <is>
-          <t>TP3</t>
-        </is>
-      </c>
-      <c r="C241" s="8" t="inlineStr">
-        <is>
-          <t>TestPoint</t>
-        </is>
-      </c>
-      <c r="D241" s="8" t="inlineStr">
-        <is>
-          <t>TestPoint_Pad_1.0x1.0mm</t>
-        </is>
-      </c>
-      <c r="E241" s="6" t="inlineStr">
-        <is>
-          <t>51.9, 90.1</t>
-        </is>
-      </c>
-      <c r="F241" s="8" t="inlineStr">
-        <is>
-          <t>不贴（测试点焊盘）</t>
-        </is>
-      </c>
-      <c r="G241" s="9" t="inlineStr"/>
-    </row>
-    <row r="242" ht="19" customHeight="1">
-      <c r="A242" s="6" t="inlineStr"/>
-      <c r="B242" s="7" t="inlineStr">
-        <is>
-          <t>TP4</t>
-        </is>
-      </c>
-      <c r="C242" s="8" t="inlineStr">
-        <is>
-          <t>TestPoint</t>
-        </is>
-      </c>
-      <c r="D242" s="8" t="inlineStr">
-        <is>
-          <t>TestPoint_Pad_1.0x1.0mm</t>
-        </is>
-      </c>
-      <c r="E242" s="6" t="inlineStr">
-        <is>
-          <t>51.9, 92.1</t>
-        </is>
-      </c>
-      <c r="F242" s="8" t="inlineStr">
-        <is>
-          <t>不贴（测试点焊盘）</t>
-        </is>
-      </c>
-      <c r="G242" s="9" t="inlineStr"/>
-    </row>
+      <c r="A241" s="2" t="inlineStr"/>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>SW3</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr">
+        <is>
+          <t>TS24CA</t>
+        </is>
+      </c>
+      <c r="D241" s="4" t="inlineStr">
+        <is>
+          <t>SW_TS24CA_2x4_SideAct</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>147.9, 89.1</t>
+        </is>
+      </c>
+      <c r="F241" s="4" t="inlineStr">
+        <is>
+          <t>A 电源</t>
+        </is>
+      </c>
+      <c r="G241" s="5" t="inlineStr"/>
+    </row>
+    <row r="242" ht="19" customHeight="1"/>
     <row r="243" ht="19" customHeight="1">
       <c r="A243" s="6" t="inlineStr"/>
       <c r="B243" s="7" t="inlineStr">
         <is>
-          <t>TP5</t>
+          <t>TP1</t>
         </is>
       </c>
       <c r="C243" s="8" t="inlineStr">
@@ -7290,7 +7298,7 @@
       </c>
       <c r="E243" s="6" t="inlineStr">
         <is>
-          <t>51.9, 94.2</t>
+          <t>51.9, 86.0</t>
         </is>
       </c>
       <c r="F243" s="8" t="inlineStr">
@@ -7304,7 +7312,7 @@
       <c r="A244" s="6" t="inlineStr"/>
       <c r="B244" s="7" t="inlineStr">
         <is>
-          <t>TP6</t>
+          <t>TP2</t>
         </is>
       </c>
       <c r="C244" s="8" t="inlineStr">
@@ -7319,7 +7327,7 @@
       </c>
       <c r="E244" s="6" t="inlineStr">
         <is>
-          <t>51.9, 96.2</t>
+          <t>51.9, 88.1</t>
         </is>
       </c>
       <c r="F244" s="8" t="inlineStr">
@@ -7333,7 +7341,7 @@
       <c r="A245" s="6" t="inlineStr"/>
       <c r="B245" s="7" t="inlineStr">
         <is>
-          <t>TP7</t>
+          <t>TP3</t>
         </is>
       </c>
       <c r="C245" s="8" t="inlineStr">
@@ -7348,7 +7356,7 @@
       </c>
       <c r="E245" s="6" t="inlineStr">
         <is>
-          <t>51.9, 98.2</t>
+          <t>51.9, 90.1</t>
         </is>
       </c>
       <c r="F245" s="8" t="inlineStr">
@@ -7358,32 +7366,60 @@
       </c>
       <c r="G245" s="9" t="inlineStr"/>
     </row>
-    <row r="246" ht="19" customHeight="1"/>
+    <row r="246" ht="19" customHeight="1">
+      <c r="A246" s="6" t="inlineStr"/>
+      <c r="B246" s="7" t="inlineStr">
+        <is>
+          <t>TP4</t>
+        </is>
+      </c>
+      <c r="C246" s="8" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="D246" s="8" t="inlineStr">
+        <is>
+          <t>TestPoint_Pad_1.0x1.0mm</t>
+        </is>
+      </c>
+      <c r="E246" s="6" t="inlineStr">
+        <is>
+          <t>51.9, 92.1</t>
+        </is>
+      </c>
+      <c r="F246" s="8" t="inlineStr">
+        <is>
+          <t>不贴（测试点焊盘）</t>
+        </is>
+      </c>
+      <c r="G246" s="9" t="inlineStr"/>
+    </row>
     <row r="247" ht="19" customHeight="1">
       <c r="A247" s="6" t="inlineStr"/>
       <c r="B247" s="7" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>TP5</t>
         </is>
       </c>
       <c r="C247" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TestPoint</t>
         </is>
       </c>
       <c r="D247" s="8" t="inlineStr">
         <is>
-          <t>MountingHole_2.7mm_M2.5</t>
+          <t>TestPoint_Pad_1.0x1.0mm</t>
         </is>
       </c>
       <c r="E247" s="6" t="inlineStr">
         <is>
-          <t>54.0, 56.0</t>
+          <t>51.9, 94.2</t>
         </is>
       </c>
       <c r="F247" s="8" t="inlineStr">
         <is>
-          <t>不贴（安装孔）</t>
+          <t>不贴（测试点焊盘）</t>
         </is>
       </c>
       <c r="G247" s="9" t="inlineStr"/>
@@ -7392,27 +7428,27 @@
       <c r="A248" s="6" t="inlineStr"/>
       <c r="B248" s="7" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>TP6</t>
         </is>
       </c>
       <c r="C248" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TestPoint</t>
         </is>
       </c>
       <c r="D248" s="8" t="inlineStr">
         <is>
-          <t>MountingHole_2.7mm_M2.5</t>
+          <t>TestPoint_Pad_1.0x1.0mm</t>
         </is>
       </c>
       <c r="E248" s="6" t="inlineStr">
         <is>
-          <t>146.0, 56.0</t>
+          <t>51.9, 96.2</t>
         </is>
       </c>
       <c r="F248" s="8" t="inlineStr">
         <is>
-          <t>不贴（安装孔）</t>
+          <t>不贴（测试点焊盘）</t>
         </is>
       </c>
       <c r="G248" s="9" t="inlineStr"/>
@@ -7421,119 +7457,207 @@
       <c r="A249" s="6" t="inlineStr"/>
       <c r="B249" s="7" t="inlineStr">
         <is>
+          <t>TP7</t>
+        </is>
+      </c>
+      <c r="C249" s="8" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="D249" s="8" t="inlineStr">
+        <is>
+          <t>TestPoint_Pad_1.0x1.0mm</t>
+        </is>
+      </c>
+      <c r="E249" s="6" t="inlineStr">
+        <is>
+          <t>51.9, 98.2</t>
+        </is>
+      </c>
+      <c r="F249" s="8" t="inlineStr">
+        <is>
+          <t>不贴（测试点焊盘）</t>
+        </is>
+      </c>
+      <c r="G249" s="9" t="inlineStr"/>
+    </row>
+    <row r="250" ht="19" customHeight="1"/>
+    <row r="251" ht="19" customHeight="1">
+      <c r="A251" s="6" t="inlineStr"/>
+      <c r="B251" s="7" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C251" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D251" s="8" t="inlineStr">
+        <is>
+          <t>MountingHole_2.7mm_M2.5</t>
+        </is>
+      </c>
+      <c r="E251" s="6" t="inlineStr">
+        <is>
+          <t>54.0, 56.0</t>
+        </is>
+      </c>
+      <c r="F251" s="8" t="inlineStr">
+        <is>
+          <t>不贴（安装孔）</t>
+        </is>
+      </c>
+      <c r="G251" s="9" t="inlineStr"/>
+    </row>
+    <row r="252" ht="19" customHeight="1">
+      <c r="A252" s="6" t="inlineStr"/>
+      <c r="B252" s="7" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C252" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D252" s="8" t="inlineStr">
+        <is>
+          <t>MountingHole_2.7mm_M2.5</t>
+        </is>
+      </c>
+      <c r="E252" s="6" t="inlineStr">
+        <is>
+          <t>146.0, 56.0</t>
+        </is>
+      </c>
+      <c r="F252" s="8" t="inlineStr">
+        <is>
+          <t>不贴（安装孔）</t>
+        </is>
+      </c>
+      <c r="G252" s="9" t="inlineStr"/>
+    </row>
+    <row r="253" ht="19" customHeight="1">
+      <c r="A253" s="6" t="inlineStr"/>
+      <c r="B253" s="7" t="inlineStr">
+        <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="C249" s="8" t="inlineStr">
+      <c r="C253" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D249" s="8" t="inlineStr">
+      <c r="D253" s="8" t="inlineStr">
         <is>
           <t>MountingHole_2.7mm_M2.5</t>
         </is>
       </c>
-      <c r="E249" s="6" t="inlineStr">
+      <c r="E253" s="6" t="inlineStr">
         <is>
           <t>54.0, 106.0</t>
         </is>
       </c>
-      <c r="F249" s="8" t="inlineStr">
+      <c r="F253" s="8" t="inlineStr">
         <is>
           <t>不贴（安装孔）</t>
         </is>
       </c>
-      <c r="G249" s="9" t="inlineStr"/>
-    </row>
-    <row r="250" ht="19" customHeight="1">
-      <c r="A250" s="6" t="inlineStr"/>
-      <c r="B250" s="7" t="inlineStr">
+      <c r="G253" s="9" t="inlineStr"/>
+    </row>
+    <row r="254" ht="19" customHeight="1">
+      <c r="A254" s="6" t="inlineStr"/>
+      <c r="B254" s="7" t="inlineStr">
         <is>
           <t>H4</t>
         </is>
       </c>
-      <c r="C250" s="8" t="inlineStr">
+      <c r="C254" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D250" s="8" t="inlineStr">
+      <c r="D254" s="8" t="inlineStr">
         <is>
           <t>MountingHole_2.7mm_M2.5</t>
         </is>
       </c>
-      <c r="E250" s="6" t="inlineStr">
+      <c r="E254" s="6" t="inlineStr">
         <is>
           <t>146.0, 106.0</t>
         </is>
       </c>
-      <c r="F250" s="8" t="inlineStr">
+      <c r="F254" s="8" t="inlineStr">
         <is>
           <t>不贴（安装孔）</t>
         </is>
       </c>
-      <c r="G250" s="9" t="inlineStr"/>
-    </row>
-    <row r="251" ht="19" customHeight="1"/>
-    <row r="252" ht="19" customHeight="1">
-      <c r="A252" s="2" t="inlineStr"/>
-      <c r="B252" s="3" t="inlineStr">
+      <c r="G254" s="9" t="inlineStr"/>
+    </row>
+    <row r="255" ht="19" customHeight="1"/>
+    <row r="256" ht="19" customHeight="1">
+      <c r="A256" s="2" t="inlineStr"/>
+      <c r="B256" s="3" t="inlineStr">
         <is>
           <t>BT1</t>
         </is>
       </c>
-      <c r="C252" s="4" t="inlineStr">
+      <c r="C256" s="4" t="inlineStr">
         <is>
           <t>MS621FE-FL11E(选贴)</t>
         </is>
       </c>
-      <c r="D252" s="4" t="inlineStr">
+      <c r="D256" s="4" t="inlineStr">
         <is>
           <t>MS621FE-FL11E</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="E256" s="2" t="inlineStr">
         <is>
           <t>138.8, 105.1</t>
         </is>
       </c>
-      <c r="F252" s="4" t="inlineStr">
+      <c r="F256" s="4" t="inlineStr">
         <is>
           <t>A 电源</t>
         </is>
       </c>
-      <c r="G252" s="5" t="inlineStr"/>
-    </row>
-    <row r="253" ht="19" customHeight="1"/>
-    <row r="254" ht="19" customHeight="1">
-      <c r="A254" s="2" t="inlineStr"/>
-      <c r="B254" s="3" t="inlineStr">
+      <c r="G256" s="5" t="inlineStr"/>
+    </row>
+    <row r="257" ht="19" customHeight="1"/>
+    <row r="258" ht="19" customHeight="1">
+      <c r="A258" s="2" t="inlineStr"/>
+      <c r="B258" s="3" t="inlineStr">
         <is>
           <t>RT1</t>
         </is>
       </c>
-      <c r="C254" s="4" t="inlineStr">
+      <c r="C258" s="4" t="inlineStr">
         <is>
           <t>NCP18XH103F03RB 10k NTC</t>
         </is>
       </c>
-      <c r="D254" s="4" t="inlineStr">
+      <c r="D258" s="4" t="inlineStr">
         <is>
           <t>R_0603_1608Metric</t>
         </is>
       </c>
-      <c r="E254" s="2" t="inlineStr">
+      <c r="E258" s="2" t="inlineStr">
         <is>
           <t>54.8, 100.9</t>
         </is>
       </c>
-      <c r="F254" s="4" t="inlineStr">
+      <c r="F258" s="4" t="inlineStr">
         <is>
           <t>A 电源</t>
         </is>
       </c>
-      <c r="G254" s="5" t="inlineStr"/>
+      <c r="G258" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <printOptions gridLines="0"/>

--- a/hardware/expansion-board-v4/CHECKLIST-V4.8.xlsx
+++ b/hardware/expansion-board-v4/CHECKLIST-V4.8.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V4.8 核对清单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="V4.8 核对清单" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'V4.8 核对清单'!$1:$1</definedName>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>J7测IFA要求后级断路；U17等未贴时C53可保留</t>
+          <t>J7测IFA要求后级断路；U16等未贴时C53可保留</t>
         </is>
       </c>
     </row>
